--- a/simple_game_test/kc_round_counts.xlsx
+++ b/simple_game_test/kc_round_counts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,310 @@
         <v>2</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>34</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>44</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>44</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>45</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>46</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>46</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>46</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>46</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>46</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>46</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/kc_round_counts.xlsx
+++ b/simple_game_test/kc_round_counts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1442,6 +1442,678 @@
         <v>4</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>47</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>47</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>47</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>47</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>47</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>49</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>49</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>49</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>49</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>49</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>50</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>51</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>51</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>51</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>51</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>51</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>51</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>52</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>52</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>52</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>52</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>52</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>52</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>53</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>53</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>53</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>53</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>53</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>53</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>54</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>54</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>54</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>54</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>54</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>54</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2</v>
+      </c>
+      <c r="D99" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>55</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>55</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>55</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>55</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>55</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>55</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/simple_game_test/kc_round_counts.xlsx
+++ b/simple_game_test/kc_round_counts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,22 @@
           <t>count</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>experimental_condition</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>domain_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>24</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -465,10 +477,22 @@
       <c r="D2" t="n">
         <v>6</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>24</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -481,10 +505,22 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
-        <v>24</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -497,10 +533,22 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
-        <v>24</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -513,10 +561,22 @@
       <c r="D5" t="n">
         <v>6</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>24</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -529,10 +589,22 @@
       <c r="D6" t="n">
         <v>2</v>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
-        <v>24</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -545,10 +617,22 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
-        <v>27</v>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -561,10 +645,22 @@
       <c r="D8" t="n">
         <v>11</v>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
-        <v>27</v>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -577,10 +673,22 @@
       <c r="D9" t="n">
         <v>3</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>27</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -593,10 +701,22 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>27</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -609,10 +729,22 @@
       <c r="D11" t="n">
         <v>8</v>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>27</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -625,10 +757,22 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>27</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -641,10 +785,22 @@
       <c r="D13" t="n">
         <v>6</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
-        <v>28</v>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -657,10 +813,22 @@
       <c r="D14" t="n">
         <v>10</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>28</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -673,10 +841,22 @@
       <c r="D15" t="n">
         <v>2</v>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>28</v>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -689,10 +869,22 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
-        <v>28</v>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -705,10 +897,22 @@
       <c r="D17" t="n">
         <v>4</v>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
-        <v>28</v>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -721,10 +925,22 @@
       <c r="D18" t="n">
         <v>7</v>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
-        <v>29</v>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -737,10 +953,22 @@
       <c r="D19" t="n">
         <v>9</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
-        <v>29</v>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -753,10 +981,22 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
-        <v>29</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -769,10 +1009,22 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
-        <v>30</v>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -785,10 +1037,22 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
-        <v>30</v>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -801,10 +1065,22 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
-        <v>30</v>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -817,10 +1093,22 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
-        <v>30</v>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -833,10 +1121,22 @@
       <c r="D25" t="n">
         <v>6</v>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
-        <v>30</v>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -849,10 +1149,22 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
-        <v>30</v>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -865,10 +1177,22 @@
       <c r="D27" t="n">
         <v>2</v>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
-        <v>31</v>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -881,10 +1205,22 @@
       <c r="D28" t="n">
         <v>7</v>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
-        <v>31</v>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -897,10 +1233,22 @@
       <c r="D29" t="n">
         <v>2</v>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
-        <v>31</v>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -913,10 +1261,22 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
-        <v>31</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -929,10 +1289,22 @@
       <c r="D31" t="n">
         <v>9</v>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -945,10 +1317,22 @@
       <c r="D32" t="n">
         <v>5</v>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
-        <v>31</v>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -961,10 +1345,22 @@
       <c r="D33" t="n">
         <v>2</v>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
-        <v>32</v>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -977,10 +1373,22 @@
       <c r="D34" t="n">
         <v>2</v>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
-        <v>32</v>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -993,10 +1401,22 @@
       <c r="D35" t="n">
         <v>3</v>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
-        <v>32</v>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1009,10 +1429,22 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
-        <v>32</v>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1025,10 +1457,22 @@
       <c r="D37" t="n">
         <v>9</v>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
-        <v>32</v>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1041,10 +1485,22 @@
       <c r="D38" t="n">
         <v>3</v>
       </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
-        <v>33</v>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1057,10 +1513,22 @@
       <c r="D39" t="n">
         <v>13</v>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
-        <v>33</v>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1073,10 +1541,22 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
-        <v>33</v>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1089,10 +1569,22 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
-        <v>33</v>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1105,10 +1597,22 @@
       <c r="D42" t="n">
         <v>15</v>
       </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
-        <v>33</v>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1121,10 +1625,22 @@
       <c r="D43" t="n">
         <v>15</v>
       </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
-        <v>33</v>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1137,10 +1653,22 @@
       <c r="D44" t="n">
         <v>2</v>
       </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
-        <v>34</v>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1153,10 +1681,22 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
-        <v>44</v>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1169,10 +1709,22 @@
       <c r="D46" t="n">
         <v>4</v>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
-        <v>44</v>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1185,10 +1737,22 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
-        <v>44</v>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1201,10 +1765,22 @@
       <c r="D48" t="n">
         <v>4</v>
       </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
-        <v>44</v>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1217,10 +1793,22 @@
       <c r="D49" t="n">
         <v>4</v>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
-        <v>44</v>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1233,10 +1821,22 @@
       <c r="D50" t="n">
         <v>4</v>
       </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
-        <v>44</v>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1249,10 +1849,22 @@
       <c r="D51" t="n">
         <v>2</v>
       </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
-        <v>45</v>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1265,10 +1877,22 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
-        <v>45</v>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1281,10 +1905,22 @@
       <c r="D53" t="n">
         <v>4</v>
       </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
-        <v>45</v>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1297,10 +1933,22 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
-        <v>45</v>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1313,10 +1961,22 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
-        <v>45</v>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1329,10 +1989,22 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
-        <v>45</v>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1345,10 +2017,22 @@
       <c r="D57" t="n">
         <v>4</v>
       </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
-        <v>46</v>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1361,10 +2045,22 @@
       <c r="D58" t="n">
         <v>4</v>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>46</v>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1377,10 +2073,22 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>46</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1393,10 +2101,22 @@
       <c r="D60" t="n">
         <v>1</v>
       </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
-        <v>46</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1409,10 +2129,22 @@
       <c r="D61" t="n">
         <v>4</v>
       </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
-        <v>46</v>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1425,10 +2157,22 @@
       <c r="D62" t="n">
         <v>4</v>
       </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
-        <v>46</v>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1441,10 +2185,22 @@
       <c r="D63" t="n">
         <v>4</v>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
-        <v>47</v>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1457,10 +2213,22 @@
       <c r="D64" t="n">
         <v>4</v>
       </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
-        <v>47</v>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1473,10 +2241,22 @@
       <c r="D65" t="n">
         <v>4</v>
       </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>47</v>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1489,10 +2269,22 @@
       <c r="D66" t="n">
         <v>2</v>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
-        <v>47</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1505,10 +2297,22 @@
       <c r="D67" t="n">
         <v>4</v>
       </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
-        <v>47</v>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1521,10 +2325,22 @@
       <c r="D68" t="n">
         <v>1</v>
       </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
-        <v>47</v>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1537,10 +2353,22 @@
       <c r="D69" t="n">
         <v>4</v>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
-        <v>49</v>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1553,10 +2381,22 @@
       <c r="D70" t="n">
         <v>4</v>
       </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
-        <v>49</v>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1569,10 +2409,22 @@
       <c r="D71" t="n">
         <v>4</v>
       </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
-        <v>49</v>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1585,10 +2437,22 @@
       <c r="D72" t="n">
         <v>2</v>
       </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>49</v>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1601,10 +2465,22 @@
       <c r="D73" t="n">
         <v>4</v>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>49</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1617,10 +2493,22 @@
       <c r="D74" t="n">
         <v>1</v>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
-        <v>50</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1633,10 +2521,22 @@
       <c r="D75" t="n">
         <v>2</v>
       </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>51</v>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1649,10 +2549,22 @@
       <c r="D76" t="n">
         <v>4</v>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>51</v>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1665,10 +2577,22 @@
       <c r="D77" t="n">
         <v>3</v>
       </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
-        <v>51</v>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1681,10 +2605,22 @@
       <c r="D78" t="n">
         <v>3</v>
       </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
-        <v>51</v>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1697,10 +2633,22 @@
       <c r="D79" t="n">
         <v>4</v>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
-        <v>51</v>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1713,10 +2661,22 @@
       <c r="D80" t="n">
         <v>2</v>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
-        <v>51</v>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1729,10 +2689,22 @@
       <c r="D81" t="n">
         <v>4</v>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
-        <v>52</v>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1745,10 +2717,22 @@
       <c r="D82" t="n">
         <v>4</v>
       </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
-        <v>52</v>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1761,10 +2745,22 @@
       <c r="D83" t="n">
         <v>4</v>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>52</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1777,10 +2773,22 @@
       <c r="D84" t="n">
         <v>1</v>
       </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>52</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1793,10 +2801,22 @@
       <c r="D85" t="n">
         <v>4</v>
       </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>52</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1809,10 +2829,22 @@
       <c r="D86" t="n">
         <v>2</v>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
-        <v>52</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1825,10 +2857,22 @@
       <c r="D87" t="n">
         <v>4</v>
       </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
-        <v>53</v>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -1841,10 +2885,22 @@
       <c r="D88" t="n">
         <v>4</v>
       </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
-        <v>53</v>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -1857,10 +2913,22 @@
       <c r="D89" t="n">
         <v>4</v>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
-        <v>53</v>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -1873,10 +2941,22 @@
       <c r="D90" t="n">
         <v>1</v>
       </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
-        <v>53</v>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -1889,10 +2969,22 @@
       <c r="D91" t="n">
         <v>3</v>
       </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
-        <v>53</v>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -1905,10 +2997,22 @@
       <c r="D92" t="n">
         <v>2</v>
       </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
-        <v>53</v>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -1921,10 +3025,22 @@
       <c r="D93" t="n">
         <v>2</v>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>54</v>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -1937,10 +3053,22 @@
       <c r="D94" t="n">
         <v>3</v>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>54</v>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -1953,10 +3081,22 @@
       <c r="D95" t="n">
         <v>2</v>
       </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>54</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -1969,10 +3109,22 @@
       <c r="D96" t="n">
         <v>2</v>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>54</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -1985,10 +3137,22 @@
       <c r="D97" t="n">
         <v>4</v>
       </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
-        <v>54</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2001,10 +3165,22 @@
       <c r="D98" t="n">
         <v>1</v>
       </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
-        <v>54</v>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2017,10 +3193,22 @@
       <c r="D99" t="n">
         <v>4</v>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
-        <v>55</v>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2033,10 +3221,22 @@
       <c r="D100" t="n">
         <v>3</v>
       </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
-        <v>55</v>
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2049,10 +3249,22 @@
       <c r="D101" t="n">
         <v>3</v>
       </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
-        <v>55</v>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2065,10 +3277,22 @@
       <c r="D102" t="n">
         <v>1</v>
       </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
-        <v>55</v>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2081,10 +3305,22 @@
       <c r="D103" t="n">
         <v>4</v>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
-        <v>55</v>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2097,10 +3333,22 @@
       <c r="D104" t="n">
         <v>2</v>
       </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
-        <v>55</v>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2112,6 +3360,464 @@
       </c>
       <c r="D105" t="n">
         <v>4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" t="n">
+        <v>4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/simple_game_test/kc_round_counts.xlsx
+++ b/simple_game_test/kc_round_counts.xlsx
@@ -475,7 +475,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -811,11 +811,11 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -923,11 +923,11 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -951,11 +951,11 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1455,11 +1455,11 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1511,11 +1511,11 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1595,11 +1595,11 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1623,11 +1623,11 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1681,16 +1681,8 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>joint_belief</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>sb-at</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1877,16 +1869,8 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1905,16 +1889,8 @@
       <c r="D53" t="n">
         <v>4</v>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1933,16 +1909,8 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1961,16 +1929,8 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1989,16 +1949,8 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2017,16 +1969,8 @@
       <c r="D57" t="n">
         <v>4</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>individual_belief_high</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>at-sb</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2047,7 +1991,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2075,7 +2019,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2103,7 +2047,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2131,7 +2075,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2159,7 +2103,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2187,7 +2131,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2383,7 +2327,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2411,7 +2355,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2439,7 +2383,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2467,7 +2411,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2495,7 +2439,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2719,7 +2663,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2747,7 +2691,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2775,7 +2719,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2803,7 +2747,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2831,7 +2775,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2859,7 +2803,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2887,7 +2831,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2915,7 +2859,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2943,7 +2887,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2971,7 +2915,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2999,7 +2943,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3027,7 +2971,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3391,7 +3335,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -3419,7 +3363,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3447,7 +3391,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3475,7 +3419,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3503,7 +3447,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3531,7 +3475,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>individual_belief_high</t>
+          <t>common_belief</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3559,7 +3503,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3587,7 +3531,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3615,7 +3559,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3643,7 +3587,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3671,7 +3615,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3699,7 +3643,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>joint_belief</t>
+          <t>individual_belief_low</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">

--- a/simple_game_test/kc_round_counts.xlsx
+++ b/simple_game_test/kc_round_counts.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3764,6 +3764,578 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>individual_belief_high</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" t="n">
+        <v>4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2</v>
+      </c>
+      <c r="D127" t="n">
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2</v>
+      </c>
+      <c r="D130" t="n">
+        <v>4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>common_belief</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>joint_belief</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>sb-at</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" t="n">
+        <v>4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>at</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>sb</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" t="n">
+        <v>4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>individual_belief_low</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>at-sb</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
